--- a/CardGameTable/Table/EquipmentDataTable.xlsx
+++ b/CardGameTable/Table/EquipmentDataTable.xlsx
@@ -1,17 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProjects\CardGame\CardGameTable\Table\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B1ED3C-AAB3-4058-B71F-4AB60E343187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="38280" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="EquipmentData" sheetId="1" r:id="rId5"/>
+    <sheet name="EquipmentData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="78">
   <si>
     <t>id</t>
   </si>
@@ -242,27 +251,47 @@
   </si>
   <si>
     <t>STAT_AMMO_CAP</t>
+  </si>
+  <si>
+    <t>Textures/Icon/Equipment/equip_weapon_sniper</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -270,46 +299,45 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -499,21 +527,24 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:O17"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="20.5"/>
-    <col customWidth="1" min="6" max="6" width="35.88"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="35.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -560,9 +591,9 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
-        <v>10001.0</v>
+        <v>10001</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>9</v>
@@ -574,7 +605,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>12</v>
@@ -583,7 +614,7 @@
         <v>13</v>
       </c>
       <c r="H2" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -594,9 +625,9 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
-        <v>10002.0</v>
+        <v>10002</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>15</v>
@@ -608,7 +639,7 @@
         <v>11</v>
       </c>
       <c r="E3" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>17</v>
@@ -617,7 +648,7 @@
         <v>13</v>
       </c>
       <c r="H3" s="1">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
@@ -631,9 +662,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
-        <v>10003.0</v>
+        <v>10003</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>19</v>
@@ -645,16 +676,16 @@
         <v>11</v>
       </c>
       <c r="E4" s="1">
-        <v>100.0</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>17</v>
+        <v>100</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>77</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="H4" s="1">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
@@ -662,9 +693,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
-        <v>10004.0</v>
+        <v>10004</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>22</v>
@@ -676,7 +707,7 @@
         <v>11</v>
       </c>
       <c r="E5" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>24</v>
@@ -685,7 +716,7 @@
         <v>13</v>
       </c>
       <c r="H5" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
@@ -699,9 +730,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
-        <v>30001.0</v>
+        <v>30001</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>27</v>
@@ -713,7 +744,7 @@
         <v>29</v>
       </c>
       <c r="E6" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>30</v>
@@ -722,18 +753,18 @@
         <v>31</v>
       </c>
       <c r="H6" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="1" t="s">
         <v>32</v>
       </c>
       <c r="J6" s="1">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>30002.0</v>
+        <v>30002</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>33</v>
@@ -745,7 +776,7 @@
         <v>29</v>
       </c>
       <c r="E7" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>35</v>
@@ -754,12 +785,12 @@
         <v>31</v>
       </c>
       <c r="H7" s="1">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>30003.0</v>
+        <v>30003</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>36</v>
@@ -771,7 +802,7 @@
         <v>29</v>
       </c>
       <c r="E8" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>38</v>
@@ -780,18 +811,18 @@
         <v>31</v>
       </c>
       <c r="H8" s="1">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>39</v>
       </c>
       <c r="J8" s="1">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>50101.0</v>
+        <v>50101</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>40</v>
@@ -803,7 +834,7 @@
         <v>42</v>
       </c>
       <c r="E9" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>43</v>
@@ -816,9 +847,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>50102.0</v>
+        <v>50102</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>45</v>
@@ -830,7 +861,7 @@
         <v>42</v>
       </c>
       <c r="E10" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>47</v>
@@ -843,9 +874,9 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>50103.0</v>
+        <v>50103</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>49</v>
@@ -857,7 +888,7 @@
         <v>42</v>
       </c>
       <c r="E11" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>51</v>
@@ -866,13 +897,13 @@
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-      <c r="K11" s="3" t="s">
+      <c r="K11" s="2" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>50104.0</v>
+        <v>50104</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>53</v>
@@ -884,7 +915,7 @@
         <v>42</v>
       </c>
       <c r="E12" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>55</v>
@@ -893,13 +924,13 @@
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
-      <c r="K12" s="3" t="s">
+      <c r="K12" s="2" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>50105.0</v>
+        <v>50105</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>57</v>
@@ -911,7 +942,7 @@
         <v>42</v>
       </c>
       <c r="E13" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>59</v>
@@ -920,13 +951,13 @@
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
-      <c r="K13" s="3" t="s">
+      <c r="K13" s="2" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>50201.0</v>
+        <v>50201</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>61</v>
@@ -938,7 +969,7 @@
         <v>42</v>
       </c>
       <c r="E14" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>63</v>
@@ -951,9 +982,9 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>50301.0</v>
+        <v>50301</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>65</v>
@@ -965,7 +996,7 @@
         <v>42</v>
       </c>
       <c r="E15" s="1">
-        <v>50.0</v>
+        <v>50</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>67</v>
@@ -978,9 +1009,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>60101.0</v>
+        <v>60101</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>69</v>
@@ -992,7 +1023,7 @@
         <v>42</v>
       </c>
       <c r="E16" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>71</v>
@@ -1001,12 +1032,12 @@
         <v>72</v>
       </c>
       <c r="H16" s="1">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>60102.0</v>
+        <v>60102</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>73</v>
@@ -1018,7 +1049,7 @@
         <v>42</v>
       </c>
       <c r="E17" s="1">
-        <v>100.0</v>
+        <v>100</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>75</v>
@@ -1027,10 +1058,11 @@
         <v>76</v>
       </c>
       <c r="H17" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <phoneticPr fontId="3" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/CardGameTable/Table/EquipmentDataTable.xlsx
+++ b/CardGameTable/Table/EquipmentDataTable.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\UnityProjects\CardGame\CardGameTable\Table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23B1ED3C-AAB3-4058-B71F-4AB60E343187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E540DAC2-9132-4062-AC90-49E834C45A90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="1560" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EquipmentData" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="78">
   <si>
     <t>id</t>
   </si>
@@ -616,8 +616,12 @@
       <c r="H2" s="1">
         <v>1</v>
       </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
+      <c r="I2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J2" s="1">
+        <v>2</v>
+      </c>
       <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
@@ -650,8 +654,12 @@
       <c r="H3" s="1">
         <v>2</v>
       </c>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
+      <c r="I3" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J3" s="1">
+        <v>3</v>
+      </c>
       <c r="K3" s="1" t="s">
         <v>18</v>
       </c>
@@ -687,8 +695,12 @@
       <c r="H4" s="1">
         <v>5</v>
       </c>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
+      <c r="I4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" s="1">
+        <v>2</v>
+      </c>
       <c r="K4" s="1" t="s">
         <v>21</v>
       </c>
@@ -718,8 +730,12 @@
       <c r="H5" s="1">
         <v>3</v>
       </c>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+      <c r="I5" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="J5" s="1">
+        <v>2</v>
+      </c>
       <c r="K5" s="1" t="s">
         <v>25</v>
       </c>
